--- a/data/trans_dic/IP1007-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1007-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen trastornos convulsivos</t>
+          <t>Menores que padecen trastornos convulsivos (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,59</t>
+          <t>0,43; 3,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,02</t>
+          <t>0,22; 2,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,42 +1008,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,81</t>
+          <t>0,08; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,98</t>
+          <t>0,17; 0,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,5</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,71</t>
+          <t>0,08; 0,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,7</t>
+          <t>0,16; 0,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,4</t>
+          <t>0,04; 0,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,55</t>
+          <t>0,08; 0,52</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen trastornos convulsivos (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2498</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4818</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 7233</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3095</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3452</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4076</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6329</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5737</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3264</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3148</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3472</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2521</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2538</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2642</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>643; 5627</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>645; 6231</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2842</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3526</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4772</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4208</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3404</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4575</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1738</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5006</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2151</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>524; 4717</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 6255</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1256; 6994</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4299</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>628; 5923</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2275; 9594</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>569; 5723</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1157; 7500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1007-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1007-Habitat-trans_dic.xlsx
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,76</t>
+          <t>0,43; 4,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,17</t>
+          <t>0,25; 2,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
     </row>
@@ -1118,42 +1118,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,69</t>
+          <t>0,08; 0,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,97</t>
+          <t>0,17; 1,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,8</t>
+          <t>0,08; 0,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,68</t>
+          <t>0,17; 0,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,39</t>
+          <t>0,04; 0,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1417,27 +1417,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2498</t>
+          <t>0; 3735</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4818</t>
+          <t>0; 5183</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7233</t>
+          <t>0; 5847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3095</t>
+          <t>0; 3492</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3452</t>
+          <t>0; 4101</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4076</t>
+          <t>0; 4512</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6329</t>
+          <t>0; 5162</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5737</t>
+          <t>0; 6458</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3264</t>
+          <t>0; 2994</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3148</t>
+          <t>0; 3113</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3472</t>
+          <t>0; 2997</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2521</t>
+          <t>0; 3123</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2642</t>
+          <t>0; 2993</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>643; 5627</t>
+          <t>640; 6064</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>645; 6231</t>
+          <t>720; 6285</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2842</t>
+          <t>0; 3230</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3526</t>
+          <t>0; 3955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1931,22 +1931,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4772</t>
+          <t>0; 4028</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4208</t>
+          <t>0; 3921</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3404</t>
+          <t>0; 2620</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4575</t>
+          <t>0; 4670</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>524; 4717</t>
+          <t>523; 5144</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5008</t>
+          <t>0; 5484</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6255</t>
+          <t>0; 5816</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1256; 6994</t>
+          <t>1256; 7304</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4299</t>
+          <t>0; 3715</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>628; 5923</t>
+          <t>624; 5837</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2275; 9594</t>
+          <t>2362; 9587</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>569; 5723</t>
+          <t>567; 5833</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1157; 7500</t>
+          <t>1158; 7525</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1007-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1007-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,87%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,37 +678,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,38%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,43; 3,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,05</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,19</t>
+          <t>0,22; 2,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,37 +1118,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,76</t>
+          <t>0,17; 0,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0,08; 0,71</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,81</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,83</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,17; 1,01</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,78</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,68</t>
+          <t>0,14; 0,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,52</t>
+          <t>0,05; 0,55</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1321,22 +1321,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>616</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1163</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3735</t>
+          <t>0; 2800</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5183</t>
+          <t>0; 3509</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5847</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3492</t>
+          <t>0; 3364</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4101</t>
+          <t>0; 5342</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 6970</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4512</t>
+          <t>0; 4010</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5162</t>
+          <t>0; 5159</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6458</t>
+          <t>0; 5813</t>
         </is>
       </c>
     </row>
@@ -1474,22 +1474,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,24 +1527,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,39 +1580,39 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3322</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3582</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>0; 2994</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3113</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2997</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3123</t>
+          <t>0; 3121</t>
         </is>
       </c>
     </row>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1690,22 +1690,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>524</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2993</t>
+          <t>639; 5377</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>640; 6064</t>
+          <t>0; 2885</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>720; 6285</t>
+          <t>646; 5807</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>568</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3517</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3230</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4385</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3955</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3106</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4028</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3921</t>
+          <t>0; 3534</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2620</t>
+          <t>0; 3837</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4670</t>
+          <t>0; 4567</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1738</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1464</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1163</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>523; 5144</t>
+          <t>1259; 7086</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5484</t>
+          <t>0; 3739</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5816</t>
+          <t>622; 5324</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1256; 7304</t>
+          <t>524; 5498</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3715</t>
+          <t>0; 5622</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>624; 5837</t>
+          <t>0; 5820</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2362; 9587</t>
+          <t>1931; 9895</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>567; 5833</t>
+          <t>567; 5762</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1158; 7525</t>
+          <t>696; 7921</t>
         </is>
       </c>
     </row>
